--- a/seeded_units_2026.xlsx
+++ b/seeded_units_2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="406">
   <si>
     <t>강의년도</t>
   </si>
@@ -109,184 +109,1045 @@
     <t>대구광역시 중구 공평로 88</t>
   </si>
   <si>
+    <t>본관 2층</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>강지훈</t>
+  </si>
+  <si>
+    <t>010-6659-8953</t>
+  </si>
+  <si>
+    <t>officer99@army.mil.kr</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>세미나실</t>
+  </si>
+  <si>
+    <t>음향시설 완비</t>
+  </si>
+  <si>
+    <t>통신13연대(2026)</t>
+  </si>
+  <si>
+    <t>MND</t>
+  </si>
+  <si>
+    <t>강원특별자치도</t>
+  </si>
+  <si>
+    <t>속초시</t>
+  </si>
+  <si>
+    <t>강원특별자치도 속초시 중앙로 183</t>
+  </si>
+  <si>
+    <t>2026-01-21</t>
+  </si>
+  <si>
+    <t>2026-01-23</t>
+  </si>
+  <si>
+    <t>강주원</t>
+  </si>
+  <si>
+    <t>010-9004-2554</t>
+  </si>
+  <si>
+    <t>officer98@army.mil.kr</t>
+  </si>
+  <si>
+    <t>회의실</t>
+  </si>
+  <si>
+    <t>에어컨 가동</t>
+  </si>
+  <si>
+    <t>통신13여단(2026)</t>
+  </si>
+  <si>
+    <t>춘천시</t>
+  </si>
+  <si>
+    <t>강원특별자치도 춘천시 중앙로 1</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>2026-01-07</t>
+  </si>
+  <si>
+    <t>윤건우</t>
+  </si>
+  <si>
+    <t>010-8099-9884</t>
+  </si>
+  <si>
+    <t>officer97@army.mil.kr</t>
+  </si>
+  <si>
+    <t>교육센터</t>
+  </si>
+  <si>
+    <t>프로젝터 있음</t>
+  </si>
+  <si>
+    <t>통신13사단(2026)</t>
+  </si>
+  <si>
+    <t>Marines</t>
+  </si>
+  <si>
+    <t>대전광역시</t>
+  </si>
+  <si>
+    <t>서구</t>
+  </si>
+  <si>
+    <t>대전광역시 서구 둔산로 100</t>
+  </si>
+  <si>
+    <t>2026-02-06</t>
+  </si>
+  <si>
+    <t>2026-02-08</t>
+  </si>
+  <si>
+    <t>황건우</t>
+  </si>
+  <si>
+    <t>010-3449-9941</t>
+  </si>
+  <si>
+    <t>officer96@army.mil.kr</t>
+  </si>
+  <si>
+    <t>다목적실</t>
+  </si>
+  <si>
+    <t>통신12교육대(2026)</t>
+  </si>
+  <si>
+    <t>AirForce</t>
+  </si>
+  <si>
+    <t>경상남도</t>
+  </si>
+  <si>
+    <t>양산시</t>
+  </si>
+  <si>
+    <t>경상남도 양산시 중앙로 39</t>
+  </si>
+  <si>
+    <t>본관 5층</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>신현우</t>
+  </si>
+  <si>
+    <t>010-9329-7599</t>
+  </si>
+  <si>
+    <t>officer95@army.mil.kr</t>
+  </si>
+  <si>
+    <t>주차 가능</t>
+  </si>
+  <si>
+    <t>통신12지원단(2026)</t>
+  </si>
+  <si>
+    <t>경상북도</t>
+  </si>
+  <si>
+    <t>안동시</t>
+  </si>
+  <si>
+    <t>경상북도 안동시 퇴계로 115</t>
+  </si>
+  <si>
+    <t>본관 1층</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-02-15</t>
+  </si>
+  <si>
+    <t>이민준</t>
+  </si>
+  <si>
+    <t>010-9885-5302</t>
+  </si>
+  <si>
+    <t>officer94@army.mil.kr</t>
+  </si>
+  <si>
+    <t>체육관</t>
+  </si>
+  <si>
+    <t>통신12사령부(2026)</t>
+  </si>
+  <si>
+    <t>충청북도</t>
+  </si>
+  <si>
+    <t>괴산군</t>
+  </si>
+  <si>
+    <t>충청북도 괴산군 괴산읍 임꺽정로 90</t>
+  </si>
+  <si>
+    <t>본관 4층</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>김지호</t>
+  </si>
+  <si>
+    <t>010-7770-2998</t>
+  </si>
+  <si>
+    <t>officer93@army.mil.kr</t>
+  </si>
+  <si>
+    <t>통신12부대(2026)</t>
+  </si>
+  <si>
+    <t>서울특별시</t>
+  </si>
+  <si>
+    <t>용산구</t>
+  </si>
+  <si>
+    <t>서울특별시 용산구 한강대로 405</t>
+  </si>
+  <si>
+    <t>2026-01-27</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>강재원</t>
+  </si>
+  <si>
+    <t>010-6730-6939</t>
+  </si>
+  <si>
+    <t>officer92@army.mil.kr</t>
+  </si>
+  <si>
+    <t>추가장소2</t>
+  </si>
+  <si>
+    <t>추가장소3</t>
+  </si>
+  <si>
+    <t>통신12대대(2026)</t>
+  </si>
+  <si>
+    <t>수성구</t>
+  </si>
+  <si>
+    <t>대구광역시 수성구 동대구로 364</t>
+  </si>
+  <si>
+    <t>최재원</t>
+  </si>
+  <si>
+    <t>010-9212-7202</t>
+  </si>
+  <si>
+    <t>officer91@army.mil.kr</t>
+  </si>
+  <si>
+    <t>대강당</t>
+  </si>
+  <si>
+    <t>통신12연대(2026)</t>
+  </si>
+  <si>
+    <t>전라남도</t>
+  </si>
+  <si>
+    <t>여수시</t>
+  </si>
+  <si>
+    <t>전라남도 여수시 시청로 1</t>
+  </si>
+  <si>
+    <t>김도현</t>
+  </si>
+  <si>
+    <t>010-4427-9725</t>
+  </si>
+  <si>
+    <t>officer90@army.mil.kr</t>
+  </si>
+  <si>
+    <t>훈련장</t>
+  </si>
+  <si>
+    <t>공병12여단(2026)</t>
+  </si>
+  <si>
+    <t>인천광역시</t>
+  </si>
+  <si>
+    <t>동구</t>
+  </si>
+  <si>
+    <t>인천광역시 동구 샛골로 130</t>
+  </si>
+  <si>
     <t>본관 3층</t>
   </si>
   <si>
+    <t>2026-01-26</t>
+  </si>
+  <si>
+    <t>최우진</t>
+  </si>
+  <si>
+    <t>010-7460-8979</t>
+  </si>
+  <si>
+    <t>officer89@army.mil.kr</t>
+  </si>
+  <si>
+    <t>공병12사단(2026)</t>
+  </si>
+  <si>
+    <t>충청남도</t>
+  </si>
+  <si>
+    <t>아산시</t>
+  </si>
+  <si>
+    <t>충청남도 아산시 번영로 224</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>오도현</t>
+  </si>
+  <si>
+    <t>010-9372-7365</t>
+  </si>
+  <si>
+    <t>officer88@army.mil.kr</t>
+  </si>
+  <si>
+    <t>공병11교육대(2026)</t>
+  </si>
+  <si>
+    <t>경기도</t>
+  </si>
+  <si>
+    <t>파주시</t>
+  </si>
+  <si>
+    <t>경기도 파주시 문발로 242</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>2026-01-06</t>
+  </si>
+  <si>
+    <t>임하준</t>
+  </si>
+  <si>
+    <t>010-1556-4909</t>
+  </si>
+  <si>
+    <t>officer87@army.mil.kr</t>
+  </si>
+  <si>
+    <t>강의실</t>
+  </si>
+  <si>
+    <t>공병11지원단(2026)</t>
+  </si>
+  <si>
+    <t>수원시 영통구</t>
+  </si>
+  <si>
+    <t>경기도 수원시 영통구 광교로 156</t>
+  </si>
+  <si>
+    <t>2026-01-13</t>
+  </si>
+  <si>
+    <t>2026-01-16</t>
+  </si>
+  <si>
+    <t>2026-01-14</t>
+  </si>
+  <si>
+    <t>최태현</t>
+  </si>
+  <si>
+    <t>010-6781-5657</t>
+  </si>
+  <si>
+    <t>officer86@army.mil.kr</t>
+  </si>
+  <si>
+    <t>공병11사령부(2026)</t>
+  </si>
+  <si>
+    <t>담양군</t>
+  </si>
+  <si>
+    <t>전라남도 담양군 담양읍 추성로 1371</t>
+  </si>
+  <si>
+    <t>2026-02-14</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>임지훈</t>
+  </si>
+  <si>
+    <t>010-5302-2827</t>
+  </si>
+  <si>
+    <t>officer85@army.mil.kr</t>
+  </si>
+  <si>
+    <t>공병11부대(2026)</t>
+  </si>
+  <si>
+    <t>화성시</t>
+  </si>
+  <si>
+    <t>경기도 화성시 남양읍 시청로 159</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>2026-02-04</t>
+  </si>
+  <si>
+    <t>최지호</t>
+  </si>
+  <si>
+    <t>010-4550-7354</t>
+  </si>
+  <si>
+    <t>officer84@army.mil.kr</t>
+  </si>
+  <si>
+    <t>공병11대대(2026)</t>
+  </si>
+  <si>
+    <t>안양시 동안구</t>
+  </si>
+  <si>
+    <t>경기도 안양시 동안구 시민대로 230</t>
+  </si>
+  <si>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>윤도윤</t>
+  </si>
+  <si>
+    <t>010-7442-7333</t>
+  </si>
+  <si>
+    <t>officer83@army.mil.kr</t>
+  </si>
+  <si>
+    <t>교육관</t>
+  </si>
+  <si>
+    <t>공병11연대(2026)</t>
+  </si>
+  <si>
+    <t>보령시</t>
+  </si>
+  <si>
+    <t>충청남도 보령시 성주산로 77</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>조우진</t>
+  </si>
+  <si>
+    <t>010-7281-7307</t>
+  </si>
+  <si>
+    <t>officer82@army.mil.kr</t>
+  </si>
+  <si>
+    <t>공병11여단(2026)</t>
+  </si>
+  <si>
+    <t>전북특별자치도</t>
+  </si>
+  <si>
+    <t>남원시</t>
+  </si>
+  <si>
+    <t>전북특별자치도 남원시 시청로 60</t>
+  </si>
+  <si>
+    <t>신재원</t>
+  </si>
+  <si>
+    <t>010-7658-8125</t>
+  </si>
+  <si>
+    <t>officer81@army.mil.kr</t>
+  </si>
+  <si>
+    <t>공병11사단(2026)</t>
+  </si>
+  <si>
+    <t>Navy</t>
+  </si>
+  <si>
+    <t>관악구</t>
+  </si>
+  <si>
+    <t>서울특별시 관악구 관악로 145</t>
+  </si>
+  <si>
+    <t>2026-01-19</t>
+  </si>
+  <si>
+    <t>2026-01-22</t>
+  </si>
+  <si>
+    <t>2026-01-20</t>
+  </si>
+  <si>
+    <t>임도현</t>
+  </si>
+  <si>
+    <t>010-7037-9955</t>
+  </si>
+  <si>
+    <t>officer80@army.mil.kr</t>
+  </si>
+  <si>
+    <t>연병장</t>
+  </si>
+  <si>
+    <t>포병10교육대(2026)</t>
+  </si>
+  <si>
+    <t>전주시 덕진구</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 건산로 251</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>2026-02-21</t>
+  </si>
+  <si>
+    <t>정민준</t>
+  </si>
+  <si>
+    <t>010-4425-1564</t>
+  </si>
+  <si>
+    <t>officer79@army.mil.kr</t>
+  </si>
+  <si>
+    <t>포병10지원단(2026)</t>
+  </si>
+  <si>
+    <t>동대문구</t>
+  </si>
+  <si>
+    <t>서울특별시 동대문구 천호대로 145</t>
+  </si>
+  <si>
+    <t>권재원</t>
+  </si>
+  <si>
+    <t>010-7573-5803</t>
+  </si>
+  <si>
+    <t>officer78@army.mil.kr</t>
+  </si>
+  <si>
+    <t>포병10사령부(2026)</t>
+  </si>
+  <si>
+    <t>횡성군</t>
+  </si>
+  <si>
+    <t>강원특별자치도 횡성군 횡성로 111</t>
+  </si>
+  <si>
+    <t>서지호</t>
+  </si>
+  <si>
+    <t>010-9122-7143</t>
+  </si>
+  <si>
+    <t>officer77@army.mil.kr</t>
+  </si>
+  <si>
+    <t>포병10부대(2026)</t>
+  </si>
+  <si>
+    <t>전주시 완산구</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 효자로 225</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>임시우</t>
+  </si>
+  <si>
+    <t>010-8057-3574</t>
+  </si>
+  <si>
+    <t>officer76@army.mil.kr</t>
+  </si>
+  <si>
+    <t>포병10대대(2026)</t>
+  </si>
+  <si>
+    <t>부평구</t>
+  </si>
+  <si>
+    <t>인천광역시 부평구 부평대로 168</t>
+  </si>
+  <si>
+    <t>강현우</t>
+  </si>
+  <si>
+    <t>010-1401-8313</t>
+  </si>
+  <si>
+    <t>officer75@army.mil.kr</t>
+  </si>
+  <si>
+    <t>포병10연대(2026)</t>
+  </si>
+  <si>
+    <t>수원시 팔달구</t>
+  </si>
+  <si>
+    <t>경기도 수원시 팔달구 효원로 1</t>
+  </si>
+  <si>
+    <t>010-5841-9311</t>
+  </si>
+  <si>
+    <t>officer74@army.mil.kr</t>
+  </si>
+  <si>
+    <t>포병10여단(2026)</t>
+  </si>
+  <si>
+    <t>대전광역시 중구 중앙로 101</t>
+  </si>
+  <si>
+    <t>오시우</t>
+  </si>
+  <si>
+    <t>010-6807-8095</t>
+  </si>
+  <si>
+    <t>officer73@army.mil.kr</t>
+  </si>
+  <si>
+    <t>포병10사단(2026)</t>
+  </si>
+  <si>
+    <t>김해시</t>
+  </si>
+  <si>
+    <t>경상남도 김해시 김해대로 2401</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>김현우</t>
+  </si>
+  <si>
+    <t>010-1880-8554</t>
+  </si>
+  <si>
+    <t>officer72@army.mil.kr</t>
+  </si>
+  <si>
+    <t>포병9교육대(2026)</t>
+  </si>
+  <si>
+    <t>구미시</t>
+  </si>
+  <si>
+    <t>경상북도 구미시 송정대로 55</t>
+  </si>
+  <si>
+    <t>한지훈</t>
+  </si>
+  <si>
+    <t>010-2189-5466</t>
+  </si>
+  <si>
+    <t>officer71@army.mil.kr</t>
+  </si>
+  <si>
+    <t>포병9지원단(2026)</t>
+  </si>
+  <si>
+    <t>인천광역시 중구 신포로27번길 80</t>
+  </si>
+  <si>
+    <t>010-1701-3054</t>
+  </si>
+  <si>
+    <t>officer70@army.mil.kr</t>
+  </si>
+  <si>
+    <t>기계화9사령부(2026)</t>
+  </si>
+  <si>
+    <t>군산시</t>
+  </si>
+  <si>
+    <t>전북특별자치도 군산시 시청로 17</t>
+  </si>
+  <si>
     <t>2026-02-20</t>
   </si>
   <si>
     <t>2026-02-22</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>오하준</t>
-  </si>
-  <si>
-    <t>010-1399-4193</t>
-  </si>
-  <si>
-    <t>officer99@army.mil.kr</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>훈련장</t>
-  </si>
-  <si>
-    <t>주차 가능</t>
-  </si>
-  <si>
-    <t>통신13연대(2026)</t>
-  </si>
-  <si>
-    <t>MND</t>
-  </si>
-  <si>
-    <t>광주광역시</t>
-  </si>
-  <si>
-    <t>북구</t>
-  </si>
-  <si>
-    <t>광주광역시 북구 용봉로 77</t>
-  </si>
-  <si>
-    <t>본관 4층</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>신지호</t>
-  </si>
-  <si>
-    <t>010-9475-5750</t>
-  </si>
-  <si>
-    <t>officer98@army.mil.kr</t>
-  </si>
-  <si>
-    <t>다목적실</t>
-  </si>
-  <si>
-    <t>통신13여단(2026)</t>
-  </si>
-  <si>
-    <t>AirForce</t>
-  </si>
-  <si>
-    <t>경상북도</t>
-  </si>
-  <si>
-    <t>영주시</t>
-  </si>
-  <si>
-    <t>경상북도 영주시 시청로 1</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>정태현</t>
-  </si>
-  <si>
-    <t>010-3200-2403</t>
-  </si>
-  <si>
-    <t>officer97@army.mil.kr</t>
-  </si>
-  <si>
-    <t>프로젝터 있음</t>
-  </si>
-  <si>
-    <t>통신13사단(2026)</t>
-  </si>
-  <si>
-    <t>서구</t>
-  </si>
-  <si>
-    <t>광주광역시 서구 내방로 111</t>
-  </si>
-  <si>
-    <t>2026-02-27</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>정지호</t>
-  </si>
-  <si>
-    <t>010-2004-5597</t>
-  </si>
-  <si>
-    <t>officer96@army.mil.kr</t>
-  </si>
-  <si>
-    <t>체육관</t>
-  </si>
-  <si>
-    <t>음향시설 완비</t>
-  </si>
-  <si>
-    <t>통신12교육대(2026)</t>
-  </si>
-  <si>
-    <t>전북특별자치도</t>
-  </si>
-  <si>
-    <t>전주시 덕진구</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 건산로 251</t>
-  </si>
-  <si>
-    <t>본관 2층</t>
-  </si>
-  <si>
-    <t>2026-03-02</t>
-  </si>
-  <si>
-    <t>윤도현</t>
-  </si>
-  <si>
-    <t>010-4020-2279</t>
-  </si>
-  <si>
-    <t>officer95@army.mil.kr</t>
-  </si>
-  <si>
-    <t>교육관</t>
-  </si>
-  <si>
-    <t>통신12지원단(2026)</t>
-  </si>
-  <si>
-    <t>전라남도</t>
+    <t>권시우</t>
+  </si>
+  <si>
+    <t>010-9987-5749</t>
+  </si>
+  <si>
+    <t>officer69@army.mil.kr</t>
+  </si>
+  <si>
+    <t>기계화9부대(2026)</t>
+  </si>
+  <si>
+    <t>성남시 분당구</t>
+  </si>
+  <si>
+    <t>경기도 성남시 분당구 판교역로 166</t>
+  </si>
+  <si>
+    <t>오우진</t>
+  </si>
+  <si>
+    <t>010-1085-2577</t>
+  </si>
+  <si>
+    <t>officer68@army.mil.kr</t>
+  </si>
+  <si>
+    <t>기계화9대대(2026)</t>
+  </si>
+  <si>
+    <t>대덕구</t>
+  </si>
+  <si>
+    <t>대전광역시 대덕구 대전로1033번길 20</t>
+  </si>
+  <si>
+    <t>황도현</t>
+  </si>
+  <si>
+    <t>010-9778-2497</t>
+  </si>
+  <si>
+    <t>officer67@army.mil.kr</t>
+  </si>
+  <si>
+    <t>기계화9연대(2026)</t>
+  </si>
+  <si>
+    <t>홍천군</t>
+  </si>
+  <si>
+    <t>강원특별자치도 홍천군 홍천로 49</t>
+  </si>
+  <si>
+    <t>박태현</t>
+  </si>
+  <si>
+    <t>010-6856-8847</t>
+  </si>
+  <si>
+    <t>officer66@army.mil.kr</t>
+  </si>
+  <si>
+    <t>기계화9여단(2026)</t>
+  </si>
+  <si>
+    <t>충주시</t>
+  </si>
+  <si>
+    <t>충청북도 충주시 으뜸로 21</t>
+  </si>
+  <si>
+    <t>장태현</t>
+  </si>
+  <si>
+    <t>010-8178-7186</t>
+  </si>
+  <si>
+    <t>officer65@army.mil.kr</t>
+  </si>
+  <si>
+    <t>기계화9사단(2026)</t>
+  </si>
+  <si>
+    <t>경주시</t>
+  </si>
+  <si>
+    <t>경상북도 경주시 양정로 260</t>
+  </si>
+  <si>
+    <t>박성민</t>
+  </si>
+  <si>
+    <t>010-4480-1410</t>
+  </si>
+  <si>
+    <t>officer64@army.mil.kr</t>
+  </si>
+  <si>
+    <t>기계화8교육대(2026)</t>
+  </si>
+  <si>
+    <t>강동구</t>
+  </si>
+  <si>
+    <t>서울특별시 강동구 천호대로 1017</t>
+  </si>
+  <si>
+    <t>조재원</t>
+  </si>
+  <si>
+    <t>010-7536-7550</t>
+  </si>
+  <si>
+    <t>officer63@army.mil.kr</t>
+  </si>
+  <si>
+    <t>기계화8지원단(2026)</t>
+  </si>
+  <si>
+    <t>음성군</t>
+  </si>
+  <si>
+    <t>충청북도 음성군 음성읍 수정로 38</t>
+  </si>
+  <si>
+    <t>윤지호</t>
+  </si>
+  <si>
+    <t>010-5426-4087</t>
+  </si>
+  <si>
+    <t>officer62@army.mil.kr</t>
+  </si>
+  <si>
+    <t>기계화8사령부(2026)</t>
+  </si>
+  <si>
+    <t>천안시 동남구</t>
+  </si>
+  <si>
+    <t>충청남도 천안시 동남구 대흥로 215</t>
+  </si>
+  <si>
+    <t>장도윤</t>
+  </si>
+  <si>
+    <t>010-2051-1784</t>
+  </si>
+  <si>
+    <t>officer61@army.mil.kr</t>
+  </si>
+  <si>
+    <t>기계화8부대(2026)</t>
+  </si>
+  <si>
+    <t>정읍시</t>
+  </si>
+  <si>
+    <t>전북특별자치도 정읍시 충정로 379</t>
+  </si>
+  <si>
+    <t>이우진</t>
+  </si>
+  <si>
+    <t>010-9460-5537</t>
+  </si>
+  <si>
+    <t>officer60@army.mil.kr</t>
+  </si>
+  <si>
+    <t>특전8대대(2026)</t>
+  </si>
+  <si>
+    <t>김포시</t>
+  </si>
+  <si>
+    <t>경기도 김포시 걸포로 170</t>
+  </si>
+  <si>
+    <t>한민준</t>
+  </si>
+  <si>
+    <t>010-5343-1406</t>
+  </si>
+  <si>
+    <t>officer59@army.mil.kr</t>
+  </si>
+  <si>
+    <t>특전8연대(2026)</t>
+  </si>
+  <si>
+    <t>제천시</t>
+  </si>
+  <si>
+    <t>충청북도 제천시 내토로 295</t>
+  </si>
+  <si>
+    <t>최민준</t>
+  </si>
+  <si>
+    <t>010-5958-7603</t>
+  </si>
+  <si>
+    <t>officer58@army.mil.kr</t>
+  </si>
+  <si>
+    <t>특전8여단(2026)</t>
+  </si>
+  <si>
+    <t>계룡시</t>
+  </si>
+  <si>
+    <t>충청남도 계룡시 장안로 46</t>
+  </si>
+  <si>
+    <t>황민준</t>
+  </si>
+  <si>
+    <t>010-3614-5521</t>
+  </si>
+  <si>
+    <t>officer57@army.mil.kr</t>
+  </si>
+  <si>
+    <t>특전8사단(2026)</t>
+  </si>
+  <si>
+    <t>천안시 서북구</t>
+  </si>
+  <si>
+    <t>충청남도 천안시 서북구 번영로 208</t>
+  </si>
+  <si>
+    <t>이주원</t>
+  </si>
+  <si>
+    <t>010-9104-2126</t>
+  </si>
+  <si>
+    <t>officer56@army.mil.kr</t>
+  </si>
+  <si>
+    <t>특전7교육대(2026)</t>
+  </si>
+  <si>
+    <t>의정부시</t>
+  </si>
+  <si>
+    <t>경기도 의정부시 청사로 1</t>
+  </si>
+  <si>
+    <t>윤민준</t>
+  </si>
+  <si>
+    <t>010-6074-9368</t>
+  </si>
+  <si>
+    <t>officer55@army.mil.kr</t>
+  </si>
+  <si>
+    <t>특전7지원단(2026)</t>
   </si>
   <si>
     <t>순천시</t>
@@ -295,724 +1156,64 @@
     <t>전라남도 순천시 장명로 30</t>
   </si>
   <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>2026-02-21</t>
-  </si>
-  <si>
-    <t>정주원</t>
-  </si>
-  <si>
-    <t>010-9652-7000</t>
-  </si>
-  <si>
-    <t>officer94@army.mil.kr</t>
-  </si>
-  <si>
-    <t>통신12사령부(2026)</t>
-  </si>
-  <si>
-    <t>담양군</t>
-  </si>
-  <si>
-    <t>전라남도 담양군 담양읍 추성로 1371</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-15</t>
-  </si>
-  <si>
-    <t>권태현</t>
-  </si>
-  <si>
-    <t>010-1641-8024</t>
-  </si>
-  <si>
-    <t>officer93@army.mil.kr</t>
-  </si>
-  <si>
-    <t>세미나실</t>
-  </si>
-  <si>
-    <t>통신12부대(2026)</t>
-  </si>
-  <si>
-    <t>대전광역시</t>
-  </si>
-  <si>
-    <t>유성구</t>
-  </si>
-  <si>
-    <t>대전광역시 유성구 대학로 99</t>
-  </si>
-  <si>
-    <t>강재원</t>
-  </si>
-  <si>
-    <t>010-4933-7187</t>
-  </si>
-  <si>
-    <t>officer92@army.mil.kr</t>
-  </si>
-  <si>
-    <t>통신12대대(2026)</t>
-  </si>
-  <si>
-    <t>대덕구</t>
-  </si>
-  <si>
-    <t>대전광역시 대덕구 대전로1033번길 20</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>윤지훈</t>
-  </si>
-  <si>
-    <t>010-3327-9968</t>
-  </si>
-  <si>
-    <t>officer91@army.mil.kr</t>
-  </si>
-  <si>
-    <t>강의실</t>
-  </si>
-  <si>
-    <t>통신12연대(2026)</t>
-  </si>
-  <si>
-    <t>Navy</t>
-  </si>
-  <si>
-    <t>대전광역시 서구 둔산로 100</t>
-  </si>
-  <si>
-    <t>본관 1층</t>
-  </si>
-  <si>
-    <t>조지호</t>
-  </si>
-  <si>
-    <t>010-5803-5249</t>
-  </si>
-  <si>
-    <t>officer90@army.mil.kr</t>
-  </si>
-  <si>
-    <t>교육센터</t>
-  </si>
-  <si>
-    <t>공병12여단(2026)</t>
-  </si>
-  <si>
-    <t>동구</t>
-  </si>
-  <si>
-    <t>대전광역시 동구 동대전로 133</t>
-  </si>
-  <si>
-    <t>2026-02-06</t>
-  </si>
-  <si>
-    <t>2026-02-08</t>
-  </si>
-  <si>
-    <t>조태현</t>
-  </si>
-  <si>
-    <t>010-6367-8650</t>
-  </si>
-  <si>
-    <t>officer89@army.mil.kr</t>
-  </si>
-  <si>
-    <t>회의실</t>
-  </si>
-  <si>
-    <t>공병12사단(2026)</t>
-  </si>
-  <si>
-    <t>충청북도</t>
-  </si>
-  <si>
-    <t>진천군</t>
-  </si>
-  <si>
-    <t>충청북도 진천군 진천읍 중앙서로 11</t>
-  </si>
-  <si>
-    <t>김예준</t>
-  </si>
-  <si>
-    <t>010-3180-8333</t>
-  </si>
-  <si>
-    <t>officer88@army.mil.kr</t>
-  </si>
-  <si>
-    <t>연병장</t>
-  </si>
-  <si>
-    <t>에어컨 가동</t>
-  </si>
-  <si>
-    <t>공병11교육대(2026)</t>
-  </si>
-  <si>
-    <t>남원시</t>
-  </si>
-  <si>
-    <t>전북특별자치도 남원시 시청로 60</t>
-  </si>
-  <si>
-    <t>본관 5층</t>
-  </si>
-  <si>
-    <t>권도윤</t>
-  </si>
-  <si>
-    <t>010-1028-1233</t>
-  </si>
-  <si>
-    <t>officer87@army.mil.kr</t>
-  </si>
-  <si>
-    <t>공병11지원단(2026)</t>
-  </si>
-  <si>
-    <t>서울특별시</t>
-  </si>
-  <si>
-    <t>성북구</t>
-  </si>
-  <si>
-    <t>서울특별시 성북구 성북로 76</t>
-  </si>
-  <si>
-    <t>2026-01-26</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
-  </si>
-  <si>
-    <t>최현우</t>
-  </si>
-  <si>
-    <t>010-3356-9452</t>
-  </si>
-  <si>
-    <t>officer86@army.mil.kr</t>
-  </si>
-  <si>
-    <t>대강당</t>
-  </si>
-  <si>
-    <t>추가장소2</t>
-  </si>
-  <si>
-    <t>공병11사령부(2026)</t>
-  </si>
-  <si>
-    <t>경기도</t>
-  </si>
-  <si>
-    <t>용인시 처인구</t>
-  </si>
-  <si>
-    <t>경기도 용인시 처인구 중부대로 1199</t>
-  </si>
-  <si>
-    <t>2026-01-20</t>
-  </si>
-  <si>
-    <t>2026-01-23</t>
-  </si>
-  <si>
-    <t>2026-01-21</t>
-  </si>
-  <si>
-    <t>오지호</t>
-  </si>
-  <si>
-    <t>010-8895-4147</t>
-  </si>
-  <si>
-    <t>officer85@army.mil.kr</t>
-  </si>
-  <si>
-    <t>공병11부대(2026)</t>
-  </si>
-  <si>
-    <t>마포구</t>
-  </si>
-  <si>
-    <t>서울특별시 마포구 월드컵북로 396</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>오우진</t>
-  </si>
-  <si>
-    <t>010-2575-4675</t>
-  </si>
-  <si>
-    <t>officer84@army.mil.kr</t>
-  </si>
-  <si>
-    <t>공병11대대(2026)</t>
-  </si>
-  <si>
-    <t>정읍시</t>
-  </si>
-  <si>
-    <t>전북특별자치도 정읍시 충정로 379</t>
-  </si>
-  <si>
-    <t>박서준</t>
-  </si>
-  <si>
-    <t>010-1057-2747</t>
-  </si>
-  <si>
-    <t>officer83@army.mil.kr</t>
-  </si>
-  <si>
-    <t>공병11연대(2026)</t>
-  </si>
-  <si>
-    <t>Marines</t>
-  </si>
-  <si>
-    <t>종로구</t>
-  </si>
-  <si>
-    <t>서울특별시 종로구 세종대로 209</t>
-  </si>
-  <si>
-    <t>2026-01-13</t>
-  </si>
-  <si>
-    <t>2026-01-16</t>
-  </si>
-  <si>
-    <t>2026-01-14</t>
-  </si>
-  <si>
-    <t>박지훈</t>
-  </si>
-  <si>
-    <t>010-8944-6576</t>
-  </si>
-  <si>
-    <t>officer82@army.mil.kr</t>
-  </si>
-  <si>
-    <t>공병11여단(2026)</t>
-  </si>
-  <si>
-    <t>인천광역시</t>
-  </si>
-  <si>
-    <t>부평구</t>
-  </si>
-  <si>
-    <t>인천광역시 부평구 부평대로 168</t>
-  </si>
-  <si>
-    <t>박주원</t>
-  </si>
-  <si>
-    <t>010-1930-2732</t>
-  </si>
-  <si>
-    <t>officer81@army.mil.kr</t>
-  </si>
-  <si>
-    <t>공병11사단(2026)</t>
-  </si>
-  <si>
-    <t>강원특별자치도</t>
-  </si>
-  <si>
-    <t>홍천군</t>
-  </si>
-  <si>
-    <t>강원특별자치도 홍천군 홍천로 49</t>
-  </si>
-  <si>
-    <t>최도윤</t>
-  </si>
-  <si>
-    <t>010-7946-8143</t>
-  </si>
-  <si>
-    <t>officer80@army.mil.kr</t>
-  </si>
-  <si>
-    <t>포병10교육대(2026)</t>
-  </si>
-  <si>
-    <t>괴산군</t>
-  </si>
-  <si>
-    <t>충청북도 괴산군 괴산읍 임꺽정로 90</t>
-  </si>
-  <si>
-    <t>2026-02-09</t>
-  </si>
-  <si>
-    <t>한지호</t>
-  </si>
-  <si>
-    <t>010-1915-2109</t>
-  </si>
-  <si>
-    <t>officer79@army.mil.kr</t>
-  </si>
-  <si>
-    <t>포병10지원단(2026)</t>
-  </si>
-  <si>
-    <t>달서구</t>
-  </si>
-  <si>
-    <t>대구광역시 달서구 학산로 30</t>
-  </si>
-  <si>
-    <t>한우진</t>
-  </si>
-  <si>
-    <t>010-2685-1814</t>
-  </si>
-  <si>
-    <t>officer78@army.mil.kr</t>
-  </si>
-  <si>
-    <t>포병10사령부(2026)</t>
-  </si>
-  <si>
-    <t>계양구</t>
-  </si>
-  <si>
-    <t>인천광역시 계양구 계양대로 168</t>
-  </si>
-  <si>
-    <t>강서준</t>
-  </si>
-  <si>
-    <t>010-1586-1267</t>
-  </si>
-  <si>
-    <t>officer77@army.mil.kr</t>
-  </si>
-  <si>
-    <t>포병10부대(2026)</t>
-  </si>
-  <si>
-    <t>충주시</t>
-  </si>
-  <si>
-    <t>충청북도 충주시 으뜸로 21</t>
+    <t>010-4886-7713</t>
+  </si>
+  <si>
+    <t>officer54@army.mil.kr</t>
+  </si>
+  <si>
+    <t>특전7사령부(2026)</t>
+  </si>
+  <si>
+    <t>연수구</t>
+  </si>
+  <si>
+    <t>인천광역시 연수구 컨벤시아대로 165</t>
+  </si>
+  <si>
+    <t>010-2316-8856</t>
+  </si>
+  <si>
+    <t>officer53@army.mil.kr</t>
+  </si>
+  <si>
+    <t>특전7부대(2026)</t>
+  </si>
+  <si>
+    <t>포항시 남구</t>
+  </si>
+  <si>
+    <t>경상북도 포항시 남구 시청로 1</t>
+  </si>
+  <si>
+    <t>황재원</t>
+  </si>
+  <si>
+    <t>010-6701-4249</t>
+  </si>
+  <si>
+    <t>officer52@army.mil.kr</t>
+  </si>
+  <si>
+    <t>특전7대대(2026)</t>
+  </si>
+  <si>
+    <t>목포시</t>
+  </si>
+  <si>
+    <t>전라남도 목포시 평화로 29</t>
   </si>
   <si>
     <t>황현우</t>
   </si>
   <si>
-    <t>010-3880-2261</t>
-  </si>
-  <si>
-    <t>officer76@army.mil.kr</t>
-  </si>
-  <si>
-    <t>포병10대대(2026)</t>
-  </si>
-  <si>
-    <t>충청남도</t>
-  </si>
-  <si>
-    <t>서산시</t>
-  </si>
-  <si>
-    <t>충청남도 서산시 관아문길 1</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>박도윤</t>
-  </si>
-  <si>
-    <t>010-6585-5789</t>
-  </si>
-  <si>
-    <t>officer75@army.mil.kr</t>
-  </si>
-  <si>
-    <t>포병10연대(2026)</t>
-  </si>
-  <si>
-    <t>군포시</t>
-  </si>
-  <si>
-    <t>경기도 군포시 청백리길 6</t>
-  </si>
-  <si>
-    <t>2026-01-07</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>최예준</t>
-  </si>
-  <si>
-    <t>010-2914-8602</t>
-  </si>
-  <si>
-    <t>officer74@army.mil.kr</t>
-  </si>
-  <si>
-    <t>포병10여단(2026)</t>
-  </si>
-  <si>
-    <t>화성시</t>
-  </si>
-  <si>
-    <t>경기도 화성시 남양읍 시청로 159</t>
-  </si>
-  <si>
-    <t>오건우</t>
-  </si>
-  <si>
-    <t>010-9768-7934</t>
-  </si>
-  <si>
-    <t>officer73@army.mil.kr</t>
-  </si>
-  <si>
-    <t>포병10사단(2026)</t>
-  </si>
-  <si>
-    <t>원주시</t>
-  </si>
-  <si>
-    <t>강원특별자치도 원주시 서원대로 158</t>
-  </si>
-  <si>
-    <t>강성민</t>
-  </si>
-  <si>
-    <t>010-3670-8772</t>
-  </si>
-  <si>
-    <t>officer72@army.mil.kr</t>
-  </si>
-  <si>
-    <t>포병9교육대(2026)</t>
-  </si>
-  <si>
-    <t>청주시 상당구</t>
-  </si>
-  <si>
-    <t>충청북도 청주시 상당구 상당로 155</t>
-  </si>
-  <si>
-    <t>2026-01-22</t>
-  </si>
-  <si>
-    <t>임우진</t>
-  </si>
-  <si>
-    <t>010-4277-6964</t>
-  </si>
-  <si>
-    <t>officer71@army.mil.kr</t>
-  </si>
-  <si>
-    <t>포병9지원단(2026)</t>
-  </si>
-  <si>
-    <t>횡성군</t>
-  </si>
-  <si>
-    <t>강원특별자치도 횡성군 횡성로 111</t>
-  </si>
-  <si>
-    <t>최성민</t>
-  </si>
-  <si>
-    <t>010-4409-8034</t>
-  </si>
-  <si>
-    <t>officer70@army.mil.kr</t>
-  </si>
-  <si>
-    <t>기계화9사령부(2026)</t>
-  </si>
-  <si>
-    <t>익산시</t>
-  </si>
-  <si>
-    <t>전북특별자치도 익산시 인북로 140</t>
-  </si>
-  <si>
-    <t>서지호</t>
-  </si>
-  <si>
-    <t>010-4395-1414</t>
-  </si>
-  <si>
-    <t>officer69@army.mil.kr</t>
-  </si>
-  <si>
-    <t>기계화9부대(2026)</t>
-  </si>
-  <si>
-    <t>경상남도</t>
-  </si>
-  <si>
-    <t>양산시</t>
-  </si>
-  <si>
-    <t>경상남도 양산시 중앙로 39</t>
-  </si>
-  <si>
-    <t>이민준</t>
-  </si>
-  <si>
-    <t>010-3911-5178</t>
-  </si>
-  <si>
-    <t>officer68@army.mil.kr</t>
-  </si>
-  <si>
-    <t>기계화9대대(2026)</t>
-  </si>
-  <si>
-    <t>계룡시</t>
-  </si>
-  <si>
-    <t>충청남도 계룡시 장안로 46</t>
-  </si>
-  <si>
-    <t>윤예준</t>
-  </si>
-  <si>
-    <t>010-5284-6754</t>
-  </si>
-  <si>
-    <t>officer67@army.mil.kr</t>
-  </si>
-  <si>
-    <t>기계화9연대(2026)</t>
-  </si>
-  <si>
-    <t>김포시</t>
-  </si>
-  <si>
-    <t>경기도 김포시 걸포로 170</t>
-  </si>
-  <si>
-    <t>신하준</t>
-  </si>
-  <si>
-    <t>010-3638-9844</t>
-  </si>
-  <si>
-    <t>officer66@army.mil.kr</t>
-  </si>
-  <si>
-    <t>기계화9여단(2026)</t>
-  </si>
-  <si>
-    <t>공주시</t>
-  </si>
-  <si>
-    <t>충청남도 공주시 봉황로 1</t>
-  </si>
-  <si>
-    <t>윤민준</t>
-  </si>
-  <si>
-    <t>010-8377-8762</t>
-  </si>
-  <si>
-    <t>officer65@army.mil.kr</t>
-  </si>
-  <si>
-    <t>기계화9사단(2026)</t>
-  </si>
-  <si>
-    <t>평택시</t>
-  </si>
-  <si>
-    <t>경기도 평택시 평택로 51</t>
-  </si>
-  <si>
-    <t>010-4916-1565</t>
-  </si>
-  <si>
-    <t>officer64@army.mil.kr</t>
-  </si>
-  <si>
-    <t>기계화8교육대(2026)</t>
-  </si>
-  <si>
-    <t>수성구</t>
-  </si>
-  <si>
-    <t>대구광역시 수성구 동대구로 364</t>
-  </si>
-  <si>
-    <t>서도현</t>
-  </si>
-  <si>
-    <t>010-5232-8544</t>
-  </si>
-  <si>
-    <t>officer63@army.mil.kr</t>
-  </si>
-  <si>
-    <t>기계화8지원단(2026)</t>
-  </si>
-  <si>
-    <t>부천시</t>
-  </si>
-  <si>
-    <t>경기도 부천시 길주로 210</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>2026-01-06</t>
-  </si>
-  <si>
-    <t>조서준</t>
-  </si>
-  <si>
-    <t>010-6477-1338</t>
-  </si>
-  <si>
-    <t>officer62@army.mil.kr</t>
-  </si>
-  <si>
-    <t>기계화8사령부(2026)</t>
+    <t>010-4986-9597</t>
+  </si>
+  <si>
+    <t>officer51@army.mil.kr</t>
+  </si>
+  <si>
+    <t>특전7연대(2026)</t>
   </si>
   <si>
     <t>삼척시</t>
@@ -1021,214 +1222,10 @@
     <t>강원특별자치도 삼척시 중앙로 296</t>
   </si>
   <si>
-    <t>조민준</t>
-  </si>
-  <si>
-    <t>010-7887-8996</t>
-  </si>
-  <si>
-    <t>officer61@army.mil.kr</t>
-  </si>
-  <si>
-    <t>기계화8부대(2026)</t>
-  </si>
-  <si>
-    <t>수원시 팔달구</t>
-  </si>
-  <si>
-    <t>경기도 수원시 팔달구 효원로 1</t>
-  </si>
-  <si>
-    <t>황하준</t>
-  </si>
-  <si>
-    <t>010-9784-8382</t>
-  </si>
-  <si>
-    <t>officer60@army.mil.kr</t>
-  </si>
-  <si>
-    <t>특전8대대(2026)</t>
-  </si>
-  <si>
-    <t>보령시</t>
-  </si>
-  <si>
-    <t>충청남도 보령시 성주산로 77</t>
-  </si>
-  <si>
-    <t>2026-01-19</t>
-  </si>
-  <si>
-    <t>윤도윤</t>
-  </si>
-  <si>
-    <t>010-3616-2928</t>
-  </si>
-  <si>
-    <t>officer59@army.mil.kr</t>
-  </si>
-  <si>
-    <t>특전8연대(2026)</t>
-  </si>
-  <si>
-    <t>제천시</t>
-  </si>
-  <si>
-    <t>충청북도 제천시 내토로 295</t>
-  </si>
-  <si>
-    <t>2026-02-14</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>김도현</t>
-  </si>
-  <si>
-    <t>010-2348-1767</t>
-  </si>
-  <si>
-    <t>officer58@army.mil.kr</t>
-  </si>
-  <si>
-    <t>특전8여단(2026)</t>
-  </si>
-  <si>
-    <t>포항시 남구</t>
-  </si>
-  <si>
-    <t>경상북도 포항시 남구 시청로 1</t>
-  </si>
-  <si>
-    <t>김태현</t>
-  </si>
-  <si>
-    <t>010-2458-9418</t>
-  </si>
-  <si>
-    <t>officer57@army.mil.kr</t>
-  </si>
-  <si>
-    <t>특전8사단(2026)</t>
-  </si>
-  <si>
-    <t>파주시</t>
-  </si>
-  <si>
-    <t>경기도 파주시 문발로 242</t>
-  </si>
-  <si>
-    <t>장지훈</t>
-  </si>
-  <si>
-    <t>010-9249-9550</t>
-  </si>
-  <si>
-    <t>officer56@army.mil.kr</t>
-  </si>
-  <si>
-    <t>특전7교육대(2026)</t>
-  </si>
-  <si>
-    <t>연수구</t>
-  </si>
-  <si>
-    <t>인천광역시 연수구 컨벤시아대로 165</t>
-  </si>
-  <si>
-    <t>오도현</t>
-  </si>
-  <si>
-    <t>010-7523-6131</t>
-  </si>
-  <si>
-    <t>officer55@army.mil.kr</t>
-  </si>
-  <si>
-    <t>특전7지원단(2026)</t>
-  </si>
-  <si>
-    <t>영등포구</t>
-  </si>
-  <si>
-    <t>서울특별시 영등포구 여의대로 108</t>
-  </si>
-  <si>
-    <t>황도윤</t>
-  </si>
-  <si>
-    <t>010-6488-8958</t>
-  </si>
-  <si>
-    <t>officer54@army.mil.kr</t>
-  </si>
-  <si>
-    <t>추가장소3</t>
-  </si>
-  <si>
-    <t>특전7사령부(2026)</t>
-  </si>
-  <si>
-    <t>용산구</t>
-  </si>
-  <si>
-    <t>서울특별시 용산구 한강대로 405</t>
-  </si>
-  <si>
-    <t>010-7634-7254</t>
-  </si>
-  <si>
-    <t>officer53@army.mil.kr</t>
-  </si>
-  <si>
-    <t>특전7부대(2026)</t>
-  </si>
-  <si>
-    <t>김천시</t>
-  </si>
-  <si>
-    <t>경상북도 김천시 시청로 20</t>
-  </si>
-  <si>
-    <t>최지훈</t>
-  </si>
-  <si>
-    <t>010-7400-4006</t>
-  </si>
-  <si>
-    <t>officer52@army.mil.kr</t>
-  </si>
-  <si>
-    <t>특전7대대(2026)</t>
-  </si>
-  <si>
-    <t>천안시 동남구</t>
-  </si>
-  <si>
-    <t>충청남도 천안시 동남구 대흥로 215</t>
-  </si>
-  <si>
-    <t>010-2054-5049</t>
-  </si>
-  <si>
-    <t>officer51@army.mil.kr</t>
-  </si>
-  <si>
-    <t>특전7연대(2026)</t>
-  </si>
-  <si>
-    <t>구미시</t>
-  </si>
-  <si>
-    <t>경상북도 구미시 송정대로 55</t>
-  </si>
-  <si>
-    <t>김성민</t>
-  </si>
-  <si>
-    <t>010-6759-2673</t>
+    <t>이성민</t>
+  </si>
+  <si>
+    <t>010-5001-7235</t>
   </si>
   <si>
     <t>officer50@army.mil.kr</t>
@@ -1612,7 +1609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z65"/>
+  <dimension ref="A1:Z67"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1774,10 +1771,10 @@
         <v>43</v>
       </c>
       <c r="X7">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="Y7">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="Z7" t="s">
         <v>46</v>
@@ -1800,13 +1797,13 @@
         <v>51</v>
       </c>
       <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
         <v>52</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>53</v>
-      </c>
-      <c r="H8" t="s">
-        <v>54</v>
       </c>
       <c r="I8" t="s">
         <v>35</v>
@@ -1824,43 +1821,43 @@
         <v>39</v>
       </c>
       <c r="N8" t="s">
+        <v>54</v>
+      </c>
+      <c r="O8" t="s">
         <v>55</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>56</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
+        <v>43</v>
+      </c>
+      <c r="R8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S8" t="s">
+        <v>43</v>
+      </c>
+      <c r="T8" t="s">
         <v>57</v>
       </c>
-      <c r="Q8" t="s">
-        <v>43</v>
-      </c>
-      <c r="R8" t="s">
-        <v>44</v>
-      </c>
-      <c r="S8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
+        <v>35</v>
+      </c>
+      <c r="V8" t="s">
+        <v>43</v>
+      </c>
+      <c r="W8" t="s">
+        <v>43</v>
+      </c>
+      <c r="X8">
+        <v>72</v>
+      </c>
+      <c r="Y8">
+        <v>61</v>
+      </c>
+      <c r="Z8" t="s">
         <v>58</v>
-      </c>
-      <c r="U8" t="s">
-        <v>35</v>
-      </c>
-      <c r="V8" t="s">
-        <v>43</v>
-      </c>
-      <c r="W8" t="s">
-        <v>43</v>
-      </c>
-      <c r="X8">
-        <v>99</v>
-      </c>
-      <c r="Y8">
-        <v>81</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -1868,25 +1865,25 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
         <v>60</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>61</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
         <v>62</v>
       </c>
-      <c r="E9" t="s">
+      <c r="H9" t="s">
         <v>63</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" t="s">
-        <v>65</v>
       </c>
       <c r="I9" t="s">
         <v>35</v>
@@ -1904,16 +1901,16 @@
         <v>39</v>
       </c>
       <c r="N9" t="s">
+        <v>64</v>
+      </c>
+      <c r="O9" t="s">
+        <v>65</v>
+      </c>
+      <c r="P9" t="s">
         <v>66</v>
       </c>
-      <c r="O9" t="s">
-        <v>67</v>
-      </c>
-      <c r="P9" t="s">
-        <v>68</v>
-      </c>
       <c r="Q9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R9" t="s">
         <v>44</v>
@@ -1922,7 +1919,7 @@
         <v>43</v>
       </c>
       <c r="T9" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="U9" t="s">
         <v>35</v>
@@ -1934,39 +1931,39 @@
         <v>43</v>
       </c>
       <c r="X9">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="Y9">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="Z9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s">
         <v>70</v>
       </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F10" t="s">
         <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I10" t="s">
         <v>35</v>
@@ -1984,13 +1981,13 @@
         <v>39</v>
       </c>
       <c r="N10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q10" t="s">
         <v>43</v>
@@ -2002,7 +1999,7 @@
         <v>43</v>
       </c>
       <c r="T10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U10" t="s">
         <v>35</v>
@@ -2014,13 +2011,13 @@
         <v>43</v>
       </c>
       <c r="X10">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="Y10">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="Z10" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -2028,25 +2025,25 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G11" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I11" t="s">
         <v>35</v>
@@ -2064,69 +2061,69 @@
         <v>39</v>
       </c>
       <c r="N11" t="s">
+        <v>88</v>
+      </c>
+      <c r="O11" t="s">
+        <v>89</v>
+      </c>
+      <c r="P11" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>43</v>
+      </c>
+      <c r="R11" t="s">
+        <v>44</v>
+      </c>
+      <c r="S11" t="s">
+        <v>43</v>
+      </c>
+      <c r="T11" t="s">
+        <v>57</v>
+      </c>
+      <c r="U11" t="s">
+        <v>35</v>
+      </c>
+      <c r="V11" t="s">
+        <v>43</v>
+      </c>
+      <c r="W11" t="s">
+        <v>43</v>
+      </c>
+      <c r="X11">
+        <v>102</v>
+      </c>
+      <c r="Y11">
         <v>86</v>
       </c>
-      <c r="O11" t="s">
-        <v>87</v>
-      </c>
-      <c r="P11" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>43</v>
-      </c>
-      <c r="R11" t="s">
-        <v>43</v>
-      </c>
-      <c r="S11" t="s">
-        <v>43</v>
-      </c>
-      <c r="T11" t="s">
-        <v>89</v>
-      </c>
-      <c r="U11" t="s">
-        <v>35</v>
-      </c>
-      <c r="V11" t="s">
-        <v>43</v>
-      </c>
-      <c r="W11" t="s">
-        <v>43</v>
-      </c>
-      <c r="X11">
-        <v>100</v>
-      </c>
-      <c r="Y11">
-        <v>87</v>
-      </c>
       <c r="Z11" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="G12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I12" t="s">
         <v>35</v>
@@ -2144,25 +2141,25 @@
         <v>39</v>
       </c>
       <c r="N12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q12" t="s">
         <v>43</v>
       </c>
       <c r="R12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="U12" t="s">
         <v>35</v>
@@ -2174,39 +2171,39 @@
         <v>43</v>
       </c>
       <c r="X12">
-        <v>51</v>
+        <v>150</v>
       </c>
       <c r="Y12">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="Z12" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B13" t="s">
         <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="G13" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H13" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I13" t="s">
         <v>35</v>
@@ -2224,13 +2221,13 @@
         <v>39</v>
       </c>
       <c r="N13" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="O13" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="P13" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="Q13" t="s">
         <v>43</v>
@@ -2242,7 +2239,7 @@
         <v>43</v>
       </c>
       <c r="T13" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="U13" t="s">
         <v>35</v>
@@ -2254,42 +2251,42 @@
         <v>43</v>
       </c>
       <c r="X13">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="Y13">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="Z13" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G14" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="H14" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="I14" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="J14" t="s">
         <v>36</v>
@@ -2304,25 +2301,25 @@
         <v>39</v>
       </c>
       <c r="N14" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="O14" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="P14" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="Q14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
       </c>
       <c r="T14" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="U14" t="s">
         <v>35</v>
@@ -2334,10 +2331,10 @@
         <v>43</v>
       </c>
       <c r="X14">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="Y14">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="Z14" t="s">
         <v>35</v>
@@ -2345,64 +2342,64 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>115</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G15" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="I15" t="s">
         <v>35</v>
       </c>
       <c r="J15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M15" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N15" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="O15" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="P15" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="Q15" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="R15" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="T15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="U15" t="s">
         <v>35</v>
@@ -2414,76 +2411,76 @@
         <v>43</v>
       </c>
       <c r="X15">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="Y15">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="Z15" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" t="s">
+        <v>35</v>
+      </c>
+      <c r="M16" t="s">
+        <v>35</v>
+      </c>
+      <c r="N16" t="s">
+        <v>35</v>
+      </c>
+      <c r="O16" t="s">
+        <v>35</v>
+      </c>
+      <c r="P16" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>35</v>
+      </c>
+      <c r="R16" t="s">
+        <v>35</v>
+      </c>
+      <c r="S16" t="s">
+        <v>35</v>
+      </c>
+      <c r="T16" t="s">
         <v>124</v>
       </c>
-      <c r="C16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" t="s">
-        <v>125</v>
-      </c>
-      <c r="F16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G16" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" t="s">
-        <v>65</v>
-      </c>
-      <c r="I16" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" t="s">
-        <v>36</v>
-      </c>
-      <c r="K16" t="s">
-        <v>37</v>
-      </c>
-      <c r="L16" t="s">
-        <v>38</v>
-      </c>
-      <c r="M16" t="s">
-        <v>39</v>
-      </c>
-      <c r="N16" t="s">
-        <v>127</v>
-      </c>
-      <c r="O16" t="s">
-        <v>128</v>
-      </c>
-      <c r="P16" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>43</v>
-      </c>
-      <c r="R16" t="s">
-        <v>44</v>
-      </c>
-      <c r="S16" t="s">
-        <v>43</v>
-      </c>
-      <c r="T16" t="s">
-        <v>130</v>
-      </c>
       <c r="U16" t="s">
         <v>35</v>
       </c>
@@ -2494,39 +2491,39 @@
         <v>43</v>
       </c>
       <c r="X16">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="Y16">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="Z16" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B17" t="s">
         <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E17" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F17" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="G17" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="H17" t="s">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="I17" t="s">
         <v>35</v>
@@ -2544,13 +2541,13 @@
         <v>39</v>
       </c>
       <c r="N17" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="O17" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="P17" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q17" t="s">
         <v>44</v>
@@ -2562,7 +2559,7 @@
         <v>43</v>
       </c>
       <c r="T17" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="U17" t="s">
         <v>35</v>
@@ -2574,39 +2571,39 @@
         <v>43</v>
       </c>
       <c r="X17">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="Y17">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="Z17" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D18" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E18" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F18" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H18" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="I18" t="s">
         <v>35</v>
@@ -2624,25 +2621,25 @@
         <v>39</v>
       </c>
       <c r="N18" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="O18" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="P18" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="Q18" t="s">
+        <v>43</v>
+      </c>
+      <c r="R18" t="s">
         <v>44</v>
       </c>
-      <c r="R18" t="s">
-        <v>43</v>
-      </c>
       <c r="S18" t="s">
         <v>43</v>
       </c>
       <c r="T18" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="U18" t="s">
         <v>35</v>
@@ -2654,39 +2651,39 @@
         <v>43</v>
       </c>
       <c r="X18">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="Y18">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="Z18" t="s">
-        <v>148</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s">
         <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="D19" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E19" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F19" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="G19" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="H19" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="I19" t="s">
         <v>35</v>
@@ -2704,13 +2701,13 @@
         <v>39</v>
       </c>
       <c r="N19" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="O19" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="P19" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="Q19" t="s">
         <v>43</v>
@@ -2722,7 +2719,7 @@
         <v>43</v>
       </c>
       <c r="T19" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="U19" t="s">
         <v>35</v>
@@ -2734,42 +2731,42 @@
         <v>43</v>
       </c>
       <c r="X19">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="Y19">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="Z19" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B20" t="s">
         <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E20" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F20" t="s">
         <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="H20" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="I20" t="s">
-        <v>162</v>
+        <v>35</v>
       </c>
       <c r="J20" t="s">
         <v>36</v>
@@ -2784,25 +2781,25 @@
         <v>39</v>
       </c>
       <c r="N20" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="O20" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="P20" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="Q20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
       </c>
       <c r="T20" t="s">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="U20" t="s">
         <v>35</v>
@@ -2814,75 +2811,75 @@
         <v>43</v>
       </c>
       <c r="X20">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="Y20">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="Z20" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>157</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>158</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="G21" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H21" t="s">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="I21" t="s">
-        <v>35</v>
+        <v>162</v>
       </c>
       <c r="J21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L21" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M21" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N21" t="s">
-        <v>35</v>
+        <v>163</v>
       </c>
       <c r="O21" t="s">
-        <v>35</v>
+        <v>164</v>
       </c>
       <c r="P21" t="s">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="Q21" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R21" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S21" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="T21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U21" t="s">
         <v>35</v>
@@ -2894,42 +2891,42 @@
         <v>43</v>
       </c>
       <c r="X21">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="Y21">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="Z21" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>167</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" t="s">
         <v>168</v>
       </c>
-      <c r="B22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>169</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" t="s">
         <v>170</v>
       </c>
-      <c r="E22" t="s">
+      <c r="H22" t="s">
         <v>171</v>
       </c>
-      <c r="F22" t="s">
-        <v>152</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="I22" t="s">
         <v>172</v>
-      </c>
-      <c r="H22" t="s">
-        <v>173</v>
-      </c>
-      <c r="I22" t="s">
-        <v>174</v>
       </c>
       <c r="J22" t="s">
         <v>36</v>
@@ -2944,19 +2941,19 @@
         <v>39</v>
       </c>
       <c r="N22" t="s">
+        <v>173</v>
+      </c>
+      <c r="O22" t="s">
+        <v>174</v>
+      </c>
+      <c r="P22" t="s">
         <v>175</v>
       </c>
-      <c r="O22" t="s">
-        <v>176</v>
-      </c>
-      <c r="P22" t="s">
-        <v>177</v>
-      </c>
       <c r="Q22" t="s">
         <v>43</v>
       </c>
       <c r="R22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
@@ -2974,13 +2971,13 @@
         <v>43</v>
       </c>
       <c r="X22">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Y22">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Z22" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
@@ -3042,7 +3039,7 @@
         <v>35</v>
       </c>
       <c r="T23" t="s">
-        <v>167</v>
+        <v>123</v>
       </c>
       <c r="U23" t="s">
         <v>35</v>
@@ -3054,10 +3051,10 @@
         <v>43</v>
       </c>
       <c r="X23">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="Y23">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="Z23" t="s">
         <v>35</v>
@@ -3065,64 +3062,64 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>178</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>157</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G24" t="s">
-        <v>162</v>
+        <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>181</v>
+        <v>35</v>
       </c>
       <c r="I24" t="s">
-        <v>182</v>
+        <v>35</v>
       </c>
       <c r="J24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L24" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M24" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N24" t="s">
-        <v>183</v>
+        <v>35</v>
       </c>
       <c r="O24" t="s">
-        <v>184</v>
+        <v>35</v>
       </c>
       <c r="P24" t="s">
-        <v>185</v>
+        <v>35</v>
       </c>
       <c r="Q24" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="R24" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="S24" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="T24" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="U24" t="s">
         <v>35</v>
@@ -3134,10 +3131,10 @@
         <v>43</v>
       </c>
       <c r="X24">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="Y24">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="Z24" t="s">
         <v>35</v>
@@ -3145,64 +3142,64 @@
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>176</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="E25" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s">
-        <v>35</v>
+        <v>179</v>
       </c>
       <c r="H25" t="s">
-        <v>35</v>
+        <v>180</v>
       </c>
       <c r="I25" t="s">
         <v>35</v>
       </c>
       <c r="J25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K25" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L25" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M25" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N25" t="s">
-        <v>35</v>
+        <v>181</v>
       </c>
       <c r="O25" t="s">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="P25" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="Q25" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R25" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S25" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="T25" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="U25" t="s">
         <v>35</v>
@@ -3214,39 +3211,39 @@
         <v>43</v>
       </c>
       <c r="X25">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Y25">
         <v>75</v>
       </c>
       <c r="Z25" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B26" t="s">
         <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="D26" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E26" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F26" t="s">
         <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>95</v>
+        <v>187</v>
       </c>
       <c r="H26" t="s">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="I26" t="s">
         <v>35</v>
@@ -3276,13 +3273,13 @@
         <v>44</v>
       </c>
       <c r="R26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
       </c>
       <c r="T26" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="U26" t="s">
         <v>35</v>
@@ -3294,13 +3291,13 @@
         <v>43</v>
       </c>
       <c r="X26">
+        <v>118</v>
+      </c>
+      <c r="Y26">
         <v>112</v>
       </c>
-      <c r="Y26">
-        <v>109</v>
-      </c>
       <c r="Z26" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
@@ -3308,28 +3305,28 @@
         <v>192</v>
       </c>
       <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" t="s">
         <v>193</v>
       </c>
-      <c r="C27" t="s">
-        <v>157</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>194</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
+        <v>144</v>
+      </c>
+      <c r="G27" t="s">
         <v>195</v>
       </c>
-      <c r="F27" t="s">
-        <v>126</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>196</v>
       </c>
-      <c r="H27" t="s">
-        <v>197</v>
-      </c>
       <c r="I27" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="J27" t="s">
         <v>36</v>
@@ -3344,26 +3341,26 @@
         <v>39</v>
       </c>
       <c r="N27" t="s">
+        <v>197</v>
+      </c>
+      <c r="O27" t="s">
+        <v>198</v>
+      </c>
+      <c r="P27" t="s">
         <v>199</v>
       </c>
-      <c r="O27" t="s">
+      <c r="Q27" t="s">
+        <v>43</v>
+      </c>
+      <c r="R27" t="s">
+        <v>44</v>
+      </c>
+      <c r="S27" t="s">
+        <v>43</v>
+      </c>
+      <c r="T27" t="s">
         <v>200</v>
       </c>
-      <c r="P27" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>43</v>
-      </c>
-      <c r="R27" t="s">
-        <v>43</v>
-      </c>
-      <c r="S27" t="s">
-        <v>43</v>
-      </c>
-      <c r="T27" t="s">
-        <v>130</v>
-      </c>
       <c r="U27" t="s">
         <v>35</v>
       </c>
@@ -3374,75 +3371,75 @@
         <v>43</v>
       </c>
       <c r="X27">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="Y27">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="Z27" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>202</v>
       </c>
       <c r="E28" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="F28" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H28" t="s">
-        <v>35</v>
+        <v>204</v>
       </c>
       <c r="I28" t="s">
         <v>35</v>
       </c>
       <c r="J28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K28" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L28" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M28" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N28" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="O28" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="P28" t="s">
-        <v>35</v>
+        <v>207</v>
       </c>
       <c r="Q28" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R28" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="S28" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="T28" t="s">
-        <v>167</v>
+        <v>57</v>
       </c>
       <c r="U28" t="s">
         <v>35</v>
@@ -3454,39 +3451,39 @@
         <v>43</v>
       </c>
       <c r="X28">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="Y28">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="Z28" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D29" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E29" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F29" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="G29" t="s">
-        <v>160</v>
+        <v>33</v>
       </c>
       <c r="H29" t="s">
-        <v>182</v>
+        <v>34</v>
       </c>
       <c r="I29" t="s">
         <v>35</v>
@@ -3504,25 +3501,25 @@
         <v>39</v>
       </c>
       <c r="N29" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="O29" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="P29" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Q29" t="s">
         <v>43</v>
       </c>
       <c r="R29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S29" t="s">
         <v>43</v>
       </c>
       <c r="T29" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="U29" t="s">
         <v>35</v>
@@ -3534,42 +3531,42 @@
         <v>43</v>
       </c>
       <c r="X29">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="Y29">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z29" t="s">
-        <v>148</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>216</v>
       </c>
       <c r="C30" t="s">
-        <v>210</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E30" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G30" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="H30" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="I30" t="s">
-        <v>35</v>
+        <v>221</v>
       </c>
       <c r="J30" t="s">
         <v>36</v>
@@ -3584,16 +3581,16 @@
         <v>39</v>
       </c>
       <c r="N30" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="O30" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="P30" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="Q30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R30" t="s">
         <v>43</v>
@@ -3602,7 +3599,7 @@
         <v>43</v>
       </c>
       <c r="T30" t="s">
-        <v>139</v>
+        <v>225</v>
       </c>
       <c r="U30" t="s">
         <v>35</v>
@@ -3614,75 +3611,75 @@
         <v>43</v>
       </c>
       <c r="X30">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y30">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z30" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>217</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>218</v>
+        <v>35</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G31" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>219</v>
+        <v>35</v>
       </c>
       <c r="I31" t="s">
         <v>35</v>
       </c>
       <c r="J31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K31" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L31" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M31" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N31" t="s">
-        <v>220</v>
+        <v>35</v>
       </c>
       <c r="O31" t="s">
-        <v>221</v>
+        <v>35</v>
       </c>
       <c r="P31" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="Q31" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="R31" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="S31" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="T31" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="U31" t="s">
         <v>35</v>
@@ -3694,39 +3691,39 @@
         <v>43</v>
       </c>
       <c r="X31">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="Y31">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="Z31" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
+        <v>209</v>
       </c>
       <c r="D32" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E32" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G32" t="s">
-        <v>94</v>
+        <v>229</v>
       </c>
       <c r="H32" t="s">
-        <v>95</v>
+        <v>230</v>
       </c>
       <c r="I32" t="s">
         <v>35</v>
@@ -3744,13 +3741,13 @@
         <v>39</v>
       </c>
       <c r="N32" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="O32" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="P32" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Q32" t="s">
         <v>43</v>
@@ -3762,7 +3759,7 @@
         <v>43</v>
       </c>
       <c r="T32" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="U32" t="s">
         <v>35</v>
@@ -3774,42 +3771,42 @@
         <v>43</v>
       </c>
       <c r="X32">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="Y32">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="Z32" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E33" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F33" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="H33" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="I33" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="J33" t="s">
         <v>36</v>
@@ -3824,16 +3821,16 @@
         <v>39</v>
       </c>
       <c r="N33" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="O33" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="P33" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R33" t="s">
         <v>43</v>
@@ -3842,7 +3839,7 @@
         <v>43</v>
       </c>
       <c r="T33" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="U33" t="s">
         <v>35</v>
@@ -3854,75 +3851,75 @@
         <v>43</v>
       </c>
       <c r="X33">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="Y33">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="Z33" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="D34" t="s">
-        <v>236</v>
+        <v>35</v>
       </c>
       <c r="E34" t="s">
-        <v>237</v>
+        <v>35</v>
       </c>
       <c r="F34" t="s">
-        <v>152</v>
+        <v>35</v>
       </c>
       <c r="G34" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="I34" t="s">
         <v>35</v>
       </c>
       <c r="J34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K34" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L34" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M34" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N34" t="s">
-        <v>238</v>
+        <v>35</v>
       </c>
       <c r="O34" t="s">
-        <v>239</v>
+        <v>35</v>
       </c>
       <c r="P34" t="s">
-        <v>240</v>
+        <v>35</v>
       </c>
       <c r="Q34" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="R34" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="S34" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="T34" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="U34" t="s">
         <v>35</v>
@@ -3934,75 +3931,75 @@
         <v>43</v>
       </c>
       <c r="X34">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="Y34">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="Z34" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>241</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>242</v>
+        <v>35</v>
       </c>
       <c r="D35" t="s">
-        <v>243</v>
+        <v>35</v>
       </c>
       <c r="E35" t="s">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G35" t="s">
-        <v>245</v>
+        <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>198</v>
+        <v>35</v>
       </c>
       <c r="I35" t="s">
         <v>35</v>
       </c>
       <c r="J35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L35" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M35" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N35" t="s">
-        <v>246</v>
+        <v>35</v>
       </c>
       <c r="O35" t="s">
-        <v>247</v>
+        <v>35</v>
       </c>
       <c r="P35" t="s">
-        <v>248</v>
+        <v>35</v>
       </c>
       <c r="Q35" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="R35" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="S35" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="T35" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="U35" t="s">
         <v>35</v>
@@ -4014,39 +4011,39 @@
         <v>43</v>
       </c>
       <c r="X35">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="Y35">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="Z35" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B36" t="s">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>169</v>
+        <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="E36" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="G36" t="s">
-        <v>252</v>
+        <v>117</v>
       </c>
       <c r="H36" t="s">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="I36" t="s">
         <v>35</v>
@@ -4064,13 +4061,13 @@
         <v>39</v>
       </c>
       <c r="N36" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="O36" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="P36" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="Q36" t="s">
         <v>43</v>
@@ -4082,7 +4079,7 @@
         <v>43</v>
       </c>
       <c r="T36" t="s">
-        <v>107</v>
+        <v>200</v>
       </c>
       <c r="U36" t="s">
         <v>35</v>
@@ -4094,42 +4091,42 @@
         <v>43</v>
       </c>
       <c r="X36">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="Y36">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="Z36" t="s">
-        <v>148</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="B37" t="s">
-        <v>193</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="D37" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="E37" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="F37" t="s">
         <v>32</v>
       </c>
       <c r="G37" t="s">
-        <v>196</v>
+        <v>249</v>
       </c>
       <c r="H37" t="s">
-        <v>197</v>
+        <v>86</v>
       </c>
       <c r="I37" t="s">
-        <v>198</v>
+        <v>35</v>
       </c>
       <c r="J37" t="s">
         <v>36</v>
@@ -4144,25 +4141,25 @@
         <v>39</v>
       </c>
       <c r="N37" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="O37" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="P37" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="Q37" t="s">
         <v>43</v>
       </c>
       <c r="R37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S37" t="s">
         <v>43</v>
       </c>
       <c r="T37" t="s">
-        <v>89</v>
+        <v>225</v>
       </c>
       <c r="U37" t="s">
         <v>35</v>
@@ -4174,39 +4171,39 @@
         <v>43</v>
       </c>
       <c r="X37">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="Y37">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="Z37" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="B38" t="s">
         <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="D38" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="E38" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="F38" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="G38" t="s">
-        <v>245</v>
+        <v>119</v>
       </c>
       <c r="H38" t="s">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="I38" t="s">
         <v>35</v>
@@ -4224,25 +4221,25 @@
         <v>39</v>
       </c>
       <c r="N38" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="O38" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="P38" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="Q38" t="s">
         <v>43</v>
       </c>
       <c r="R38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S38" t="s">
         <v>43</v>
       </c>
       <c r="T38" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="U38" t="s">
         <v>35</v>
@@ -4254,42 +4251,42 @@
         <v>43</v>
       </c>
       <c r="X38">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="Y38">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="Z38" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B39" t="s">
-        <v>193</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="D39" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="E39" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="F39" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="G39" t="s">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="H39" t="s">
-        <v>272</v>
+        <v>53</v>
       </c>
       <c r="I39" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="J39" t="s">
         <v>36</v>
@@ -4304,16 +4301,16 @@
         <v>39</v>
       </c>
       <c r="N39" t="s">
-        <v>273</v>
+        <v>54</v>
       </c>
       <c r="O39" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="P39" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="Q39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R39" t="s">
         <v>43</v>
@@ -4322,7 +4319,7 @@
         <v>43</v>
       </c>
       <c r="T39" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="U39" t="s">
         <v>35</v>
@@ -4334,75 +4331,75 @@
         <v>43</v>
       </c>
       <c r="X39">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="Y39">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="Z39" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>276</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>210</v>
+        <v>35</v>
       </c>
       <c r="D40" t="s">
-        <v>277</v>
+        <v>35</v>
       </c>
       <c r="E40" t="s">
-        <v>278</v>
+        <v>35</v>
       </c>
       <c r="F40" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="G40" t="s">
-        <v>174</v>
+        <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>173</v>
+        <v>35</v>
       </c>
       <c r="I40" t="s">
         <v>35</v>
       </c>
       <c r="J40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K40" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L40" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M40" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N40" t="s">
-        <v>279</v>
+        <v>35</v>
       </c>
       <c r="O40" t="s">
-        <v>280</v>
+        <v>35</v>
       </c>
       <c r="P40" t="s">
-        <v>281</v>
+        <v>35</v>
       </c>
       <c r="Q40" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="R40" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="S40" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="T40" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="U40" t="s">
         <v>35</v>
@@ -4414,39 +4411,39 @@
         <v>43</v>
       </c>
       <c r="X40">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Y40">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Z40" t="s">
-        <v>148</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="B41" t="s">
         <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D41" t="s">
-        <v>283</v>
+        <v>30</v>
       </c>
       <c r="E41" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="F41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G41" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="H41" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="I41" t="s">
         <v>35</v>
@@ -4464,25 +4461,25 @@
         <v>39</v>
       </c>
       <c r="N41" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="O41" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="P41" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="Q41" t="s">
         <v>43</v>
       </c>
       <c r="R41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S41" t="s">
         <v>43</v>
       </c>
       <c r="T41" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="U41" t="s">
         <v>35</v>
@@ -4494,10 +4491,10 @@
         <v>43</v>
       </c>
       <c r="X41">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="Y41">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Z41" t="s">
         <v>46</v>
@@ -4505,28 +4502,28 @@
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="B42" t="s">
         <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="D42" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="E42" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="F42" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="G42" t="s">
-        <v>134</v>
+        <v>230</v>
       </c>
       <c r="H42" t="s">
-        <v>135</v>
+        <v>272</v>
       </c>
       <c r="I42" t="s">
         <v>35</v>
@@ -4544,25 +4541,25 @@
         <v>39</v>
       </c>
       <c r="N42" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="O42" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="P42" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="Q42" t="s">
         <v>43</v>
       </c>
       <c r="R42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S42" t="s">
         <v>43</v>
       </c>
       <c r="T42" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="U42" t="s">
         <v>35</v>
@@ -4574,39 +4571,39 @@
         <v>43</v>
       </c>
       <c r="X42">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="Y42">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="Z42" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="B43" t="s">
         <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>242</v>
+        <v>93</v>
       </c>
       <c r="D43" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="E43" t="s">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="F43" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="G43" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="H43" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I43" t="s">
         <v>35</v>
@@ -4624,25 +4621,25 @@
         <v>39</v>
       </c>
       <c r="N43" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="O43" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="P43" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="Q43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S43" t="s">
         <v>43</v>
       </c>
       <c r="T43" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="U43" t="s">
         <v>35</v>
@@ -4654,39 +4651,39 @@
         <v>43</v>
       </c>
       <c r="X43">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="Y43">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="Z43" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="B44" t="s">
         <v>28</v>
       </c>
       <c r="C44" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="D44" t="s">
-        <v>302</v>
+        <v>30</v>
       </c>
       <c r="E44" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="F44" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="G44" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="H44" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="I44" t="s">
         <v>35</v>
@@ -4704,13 +4701,13 @@
         <v>39</v>
       </c>
       <c r="N44" t="s">
-        <v>304</v>
+        <v>110</v>
       </c>
       <c r="O44" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="P44" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="Q44" t="s">
         <v>43</v>
@@ -4722,7 +4719,7 @@
         <v>43</v>
       </c>
       <c r="T44" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="U44" t="s">
         <v>35</v>
@@ -4734,39 +4731,39 @@
         <v>43</v>
       </c>
       <c r="X44">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="Y44">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="Z44" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="B45" t="s">
         <v>28</v>
       </c>
       <c r="C45" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="E45" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="F45" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="G45" t="s">
-        <v>245</v>
+        <v>289</v>
       </c>
       <c r="H45" t="s">
-        <v>198</v>
+        <v>290</v>
       </c>
       <c r="I45" t="s">
         <v>35</v>
@@ -4784,25 +4781,25 @@
         <v>39</v>
       </c>
       <c r="N45" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="O45" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="P45" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="Q45" t="s">
         <v>44</v>
       </c>
       <c r="R45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S45" t="s">
         <v>43</v>
       </c>
       <c r="T45" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="U45" t="s">
         <v>35</v>
@@ -4814,42 +4811,42 @@
         <v>43</v>
       </c>
       <c r="X45">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="Y45">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="Z45" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="B46" t="s">
         <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="E46" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="F46" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="G46" t="s">
-        <v>160</v>
+        <v>62</v>
       </c>
       <c r="H46" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="I46" t="s">
-        <v>35</v>
+        <v>162</v>
       </c>
       <c r="J46" t="s">
         <v>36</v>
@@ -4864,25 +4861,25 @@
         <v>39</v>
       </c>
       <c r="N46" t="s">
-        <v>213</v>
+        <v>297</v>
       </c>
       <c r="O46" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="P46" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="Q46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S46" t="s">
         <v>43</v>
       </c>
       <c r="T46" t="s">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="U46" t="s">
         <v>35</v>
@@ -4894,75 +4891,75 @@
         <v>43</v>
       </c>
       <c r="X46">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="Y46">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="Z46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>318</v>
+        <v>35</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D47" t="s">
-        <v>319</v>
+        <v>35</v>
       </c>
       <c r="E47" t="s">
-        <v>320</v>
+        <v>35</v>
       </c>
       <c r="F47" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G47" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="I47" t="s">
         <v>35</v>
       </c>
       <c r="J47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K47" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L47" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M47" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N47" t="s">
-        <v>321</v>
+        <v>35</v>
       </c>
       <c r="O47" t="s">
-        <v>322</v>
+        <v>35</v>
       </c>
       <c r="P47" t="s">
-        <v>323</v>
+        <v>35</v>
       </c>
       <c r="Q47" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="R47" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="S47" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="T47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="U47" t="s">
         <v>35</v>
@@ -4974,76 +4971,76 @@
         <v>43</v>
       </c>
       <c r="X47">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="Y47">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="Z47" t="s">
-        <v>148</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>324</v>
+        <v>35</v>
       </c>
       <c r="B48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" t="s">
+        <v>35</v>
+      </c>
+      <c r="F48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G48" t="s">
+        <v>35</v>
+      </c>
+      <c r="H48" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K48" t="s">
+        <v>35</v>
+      </c>
+      <c r="L48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M48" t="s">
+        <v>35</v>
+      </c>
+      <c r="N48" t="s">
+        <v>35</v>
+      </c>
+      <c r="O48" t="s">
+        <v>35</v>
+      </c>
+      <c r="P48" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>35</v>
+      </c>
+      <c r="R48" t="s">
+        <v>35</v>
+      </c>
+      <c r="S48" t="s">
+        <v>35</v>
+      </c>
+      <c r="T48" t="s">
         <v>124</v>
       </c>
-      <c r="C48" t="s">
-        <v>169</v>
-      </c>
-      <c r="D48" t="s">
-        <v>325</v>
-      </c>
-      <c r="E48" t="s">
-        <v>326</v>
-      </c>
-      <c r="F48" t="s">
-        <v>32</v>
-      </c>
-      <c r="G48" t="s">
-        <v>327</v>
-      </c>
-      <c r="H48" t="s">
-        <v>328</v>
-      </c>
-      <c r="I48" t="s">
-        <v>329</v>
-      </c>
-      <c r="J48" t="s">
-        <v>36</v>
-      </c>
-      <c r="K48" t="s">
-        <v>37</v>
-      </c>
-      <c r="L48" t="s">
-        <v>38</v>
-      </c>
-      <c r="M48" t="s">
-        <v>39</v>
-      </c>
-      <c r="N48" t="s">
-        <v>330</v>
-      </c>
-      <c r="O48" t="s">
-        <v>331</v>
-      </c>
-      <c r="P48" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>43</v>
-      </c>
-      <c r="R48" t="s">
-        <v>43</v>
-      </c>
-      <c r="S48" t="s">
-        <v>43</v>
-      </c>
-      <c r="T48" t="s">
-        <v>107</v>
-      </c>
       <c r="U48" t="s">
         <v>35</v>
       </c>
@@ -5054,10 +5051,10 @@
         <v>43</v>
       </c>
       <c r="X48">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="Y48">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="Z48" t="s">
         <v>35</v>
@@ -5065,28 +5062,28 @@
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="B49" t="s">
         <v>28</v>
       </c>
       <c r="C49" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
       <c r="D49" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="E49" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="F49" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G49" t="s">
-        <v>245</v>
+        <v>97</v>
       </c>
       <c r="H49" t="s">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="I49" t="s">
         <v>35</v>
@@ -5104,25 +5101,25 @@
         <v>39</v>
       </c>
       <c r="N49" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="O49" t="s">
-        <v>337</v>
+        <v>304</v>
       </c>
       <c r="P49" t="s">
-        <v>338</v>
+        <v>305</v>
       </c>
       <c r="Q49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S49" t="s">
         <v>43</v>
       </c>
       <c r="T49" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="U49" t="s">
         <v>35</v>
@@ -5134,42 +5131,42 @@
         <v>43</v>
       </c>
       <c r="X49">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="Y49">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="Z49" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
       <c r="B50" t="s">
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>169</v>
+        <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="E50" t="s">
-        <v>341</v>
+        <v>308</v>
       </c>
       <c r="F50" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="G50" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="H50" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="I50" t="s">
-        <v>162</v>
+        <v>35</v>
       </c>
       <c r="J50" t="s">
         <v>36</v>
@@ -5184,16 +5181,16 @@
         <v>39</v>
       </c>
       <c r="N50" t="s">
-        <v>342</v>
+        <v>309</v>
       </c>
       <c r="O50" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
       <c r="P50" t="s">
-        <v>344</v>
+        <v>311</v>
       </c>
       <c r="Q50" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R50" t="s">
         <v>43</v>
@@ -5202,7 +5199,7 @@
         <v>43</v>
       </c>
       <c r="T50" t="s">
-        <v>147</v>
+        <v>67</v>
       </c>
       <c r="U50" t="s">
         <v>35</v>
@@ -5214,75 +5211,75 @@
         <v>43</v>
       </c>
       <c r="X50">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="Y50">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="Z50" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="C51" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D51" t="s">
-        <v>35</v>
+        <v>313</v>
       </c>
       <c r="E51" t="s">
-        <v>35</v>
+        <v>314</v>
       </c>
       <c r="F51" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="G51" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H51" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="I51" t="s">
         <v>35</v>
       </c>
       <c r="J51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K51" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L51" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M51" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N51" t="s">
-        <v>35</v>
+        <v>315</v>
       </c>
       <c r="O51" t="s">
-        <v>35</v>
+        <v>316</v>
       </c>
       <c r="P51" t="s">
-        <v>35</v>
+        <v>317</v>
       </c>
       <c r="Q51" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R51" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S51" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="T51" t="s">
-        <v>167</v>
+        <v>57</v>
       </c>
       <c r="U51" t="s">
         <v>35</v>
@@ -5294,39 +5291,39 @@
         <v>43</v>
       </c>
       <c r="X51">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="Y51">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="Z51" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="B52" t="s">
-        <v>193</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>242</v>
+        <v>93</v>
       </c>
       <c r="D52" t="s">
-        <v>346</v>
+        <v>319</v>
       </c>
       <c r="E52" t="s">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="F52" t="s">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="G52" t="s">
-        <v>348</v>
+        <v>249</v>
       </c>
       <c r="H52" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="I52" t="s">
         <v>35</v>
@@ -5344,13 +5341,13 @@
         <v>39</v>
       </c>
       <c r="N52" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="O52" t="s">
-        <v>350</v>
+        <v>322</v>
       </c>
       <c r="P52" t="s">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="Q52" t="s">
         <v>43</v>
@@ -5362,7 +5359,7 @@
         <v>43</v>
       </c>
       <c r="T52" t="s">
-        <v>122</v>
+        <v>225</v>
       </c>
       <c r="U52" t="s">
         <v>35</v>
@@ -5374,42 +5371,42 @@
         <v>43</v>
       </c>
       <c r="X52">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="Y52">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="Z52" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>352</v>
+        <v>324</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="D53" t="s">
-        <v>353</v>
+        <v>325</v>
       </c>
       <c r="E53" t="s">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="F53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G53" t="s">
-        <v>355</v>
+        <v>162</v>
       </c>
       <c r="H53" t="s">
-        <v>356</v>
+        <v>204</v>
       </c>
       <c r="I53" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="J53" t="s">
         <v>36</v>
@@ -5424,13 +5421,13 @@
         <v>39</v>
       </c>
       <c r="N53" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
       <c r="O53" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="P53" t="s">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="Q53" t="s">
         <v>43</v>
@@ -5442,7 +5439,7 @@
         <v>43</v>
       </c>
       <c r="T53" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="U53" t="s">
         <v>35</v>
@@ -5454,10 +5451,10 @@
         <v>43</v>
       </c>
       <c r="X53">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="Y53">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="Z53" t="s">
         <v>46</v>
@@ -5465,64 +5462,64 @@
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>360</v>
+        <v>35</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C54" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D54" t="s">
-        <v>361</v>
+        <v>35</v>
       </c>
       <c r="E54" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="F54" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G54" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="H54" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="I54" t="s">
         <v>35</v>
       </c>
       <c r="J54" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K54" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L54" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M54" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N54" t="s">
-        <v>363</v>
+        <v>35</v>
       </c>
       <c r="O54" t="s">
-        <v>364</v>
+        <v>35</v>
       </c>
       <c r="P54" t="s">
-        <v>365</v>
+        <v>35</v>
       </c>
       <c r="Q54" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="R54" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="S54" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="T54" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="U54" t="s">
         <v>35</v>
@@ -5534,42 +5531,42 @@
         <v>43</v>
       </c>
       <c r="X54">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="Y54">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="Z54" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>366</v>
+        <v>330</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="D55" t="s">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="E55" t="s">
-        <v>368</v>
+        <v>332</v>
       </c>
       <c r="F55" t="s">
-        <v>152</v>
+        <v>32</v>
       </c>
       <c r="G55" t="s">
-        <v>162</v>
+        <v>249</v>
       </c>
       <c r="H55" t="s">
-        <v>181</v>
+        <v>86</v>
       </c>
       <c r="I55" t="s">
-        <v>182</v>
+        <v>35</v>
       </c>
       <c r="J55" t="s">
         <v>36</v>
@@ -5584,25 +5581,25 @@
         <v>39</v>
       </c>
       <c r="N55" t="s">
-        <v>369</v>
+        <v>333</v>
       </c>
       <c r="O55" t="s">
-        <v>370</v>
+        <v>334</v>
       </c>
       <c r="P55" t="s">
-        <v>371</v>
+        <v>335</v>
       </c>
       <c r="Q55" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R55" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S55" t="s">
         <v>43</v>
       </c>
       <c r="T55" t="s">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="U55" t="s">
         <v>35</v>
@@ -5614,39 +5611,39 @@
         <v>43</v>
       </c>
       <c r="X55">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="Y55">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>372</v>
+        <v>336</v>
       </c>
       <c r="B56" t="s">
-        <v>193</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="D56" t="s">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="E56" t="s">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="F56" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="G56" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="H56" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I56" t="s">
         <v>35</v>
@@ -5664,25 +5661,25 @@
         <v>39</v>
       </c>
       <c r="N56" t="s">
-        <v>375</v>
+        <v>339</v>
       </c>
       <c r="O56" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="P56" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="Q56" t="s">
         <v>43</v>
       </c>
       <c r="R56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S56" t="s">
         <v>43</v>
       </c>
       <c r="T56" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="U56" t="s">
         <v>35</v>
@@ -5694,42 +5691,42 @@
         <v>43</v>
       </c>
       <c r="X56">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="Y56">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="Z56" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C57" t="s">
-        <v>157</v>
+        <v>209</v>
       </c>
       <c r="D57" t="s">
-        <v>379</v>
+        <v>343</v>
       </c>
       <c r="E57" t="s">
-        <v>380</v>
+        <v>344</v>
       </c>
       <c r="F57" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="G57" t="s">
-        <v>162</v>
+        <v>289</v>
       </c>
       <c r="H57" t="s">
-        <v>181</v>
+        <v>290</v>
       </c>
       <c r="I57" t="s">
-        <v>182</v>
+        <v>35</v>
       </c>
       <c r="J57" t="s">
         <v>36</v>
@@ -5744,25 +5741,25 @@
         <v>39</v>
       </c>
       <c r="N57" t="s">
-        <v>381</v>
+        <v>345</v>
       </c>
       <c r="O57" t="s">
-        <v>382</v>
+        <v>346</v>
       </c>
       <c r="P57" t="s">
-        <v>383</v>
+        <v>347</v>
       </c>
       <c r="Q57" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R57" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S57" t="s">
         <v>43</v>
       </c>
       <c r="T57" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="U57" t="s">
         <v>35</v>
@@ -5774,75 +5771,75 @@
         <v>43</v>
       </c>
       <c r="X57">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="Y57">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="Z57" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>35</v>
+        <v>348</v>
       </c>
       <c r="B58" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
-        <v>35</v>
+        <v>158</v>
       </c>
       <c r="D58" t="s">
-        <v>35</v>
+        <v>349</v>
       </c>
       <c r="E58" t="s">
-        <v>35</v>
+        <v>350</v>
       </c>
       <c r="F58" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G58" t="s">
-        <v>35</v>
+        <v>221</v>
       </c>
       <c r="H58" t="s">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="I58" t="s">
         <v>35</v>
       </c>
       <c r="J58" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K58" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L58" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M58" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N58" t="s">
-        <v>35</v>
+        <v>351</v>
       </c>
       <c r="O58" t="s">
-        <v>35</v>
+        <v>352</v>
       </c>
       <c r="P58" t="s">
-        <v>35</v>
+        <v>353</v>
       </c>
       <c r="Q58" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R58" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S58" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="T58" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="U58" t="s">
         <v>35</v>
@@ -5854,75 +5851,75 @@
         <v>43</v>
       </c>
       <c r="X58">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="Y58">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="Z58" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B59" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C59" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D59" t="s">
-        <v>35</v>
+        <v>355</v>
       </c>
       <c r="E59" t="s">
-        <v>35</v>
+        <v>356</v>
       </c>
       <c r="F59" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="G59" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="H59" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="I59" t="s">
         <v>35</v>
       </c>
       <c r="J59" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K59" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L59" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M59" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N59" t="s">
-        <v>35</v>
+        <v>357</v>
       </c>
       <c r="O59" t="s">
-        <v>35</v>
+        <v>358</v>
       </c>
       <c r="P59" t="s">
-        <v>35</v>
+        <v>359</v>
       </c>
       <c r="Q59" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R59" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="S59" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="T59" t="s">
-        <v>384</v>
+        <v>139</v>
       </c>
       <c r="U59" t="s">
         <v>35</v>
@@ -5934,42 +5931,42 @@
         <v>43</v>
       </c>
       <c r="X59">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="Y59">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="Z59" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="B60" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C60" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D60" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="E60" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="F60" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="G60" t="s">
-        <v>348</v>
+        <v>170</v>
       </c>
       <c r="H60" t="s">
-        <v>272</v>
+        <v>196</v>
       </c>
       <c r="I60" t="s">
-        <v>172</v>
+        <v>35</v>
       </c>
       <c r="J60" t="s">
         <v>36</v>
@@ -5984,13 +5981,13 @@
         <v>39</v>
       </c>
       <c r="N60" t="s">
-        <v>285</v>
+        <v>363</v>
       </c>
       <c r="O60" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="P60" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="Q60" t="s">
         <v>43</v>
@@ -6002,7 +5999,7 @@
         <v>43</v>
       </c>
       <c r="T60" t="s">
-        <v>89</v>
+        <v>225</v>
       </c>
       <c r="U60" t="s">
         <v>35</v>
@@ -6014,75 +6011,75 @@
         <v>43</v>
       </c>
       <c r="X60">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="Y60">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="Z60" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>35</v>
+        <v>366</v>
       </c>
       <c r="B61" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="D61" t="s">
-        <v>35</v>
+        <v>367</v>
       </c>
       <c r="E61" t="s">
-        <v>35</v>
+        <v>368</v>
       </c>
       <c r="F61" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="G61" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H61" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="I61" t="s">
         <v>35</v>
       </c>
       <c r="J61" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K61" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L61" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M61" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N61" t="s">
-        <v>35</v>
+        <v>369</v>
       </c>
       <c r="O61" t="s">
-        <v>35</v>
+        <v>370</v>
       </c>
       <c r="P61" t="s">
-        <v>35</v>
+        <v>371</v>
       </c>
       <c r="Q61" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R61" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S61" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="T61" t="s">
-        <v>167</v>
+        <v>102</v>
       </c>
       <c r="U61" t="s">
         <v>35</v>
@@ -6094,75 +6091,75 @@
         <v>43</v>
       </c>
       <c r="X61">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="Y61">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="Z61" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>35</v>
+        <v>372</v>
       </c>
       <c r="B62" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="C62" t="s">
-        <v>35</v>
+        <v>158</v>
       </c>
       <c r="D62" t="s">
-        <v>35</v>
+        <v>373</v>
       </c>
       <c r="E62" t="s">
-        <v>35</v>
+        <v>374</v>
       </c>
       <c r="F62" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="G62" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="H62" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
       <c r="I62" t="s">
         <v>35</v>
       </c>
       <c r="J62" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K62" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L62" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M62" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N62" t="s">
-        <v>35</v>
+        <v>375</v>
       </c>
       <c r="O62" t="s">
-        <v>35</v>
+        <v>376</v>
       </c>
       <c r="P62" t="s">
-        <v>35</v>
+        <v>377</v>
       </c>
       <c r="Q62" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R62" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S62" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="T62" t="s">
-        <v>384</v>
+        <v>79</v>
       </c>
       <c r="U62" t="s">
         <v>35</v>
@@ -6174,39 +6171,39 @@
         <v>43</v>
       </c>
       <c r="X62">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="Y62">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="Z62" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>216</v>
       </c>
       <c r="C63" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="D63" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="E63" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="F63" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="G63" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="H63" t="s">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="I63" t="s">
         <v>35</v>
@@ -6224,13 +6221,13 @@
         <v>39</v>
       </c>
       <c r="N63" t="s">
-        <v>393</v>
+        <v>357</v>
       </c>
       <c r="O63" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="P63" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="Q63" t="s">
         <v>43</v>
@@ -6242,7 +6239,7 @@
         <v>43</v>
       </c>
       <c r="T63" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="U63" t="s">
         <v>35</v>
@@ -6254,39 +6251,39 @@
         <v>43</v>
       </c>
       <c r="X63">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="Y63">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="Z63" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="B64" t="s">
         <v>28</v>
       </c>
       <c r="C64" t="s">
-        <v>242</v>
+        <v>141</v>
       </c>
       <c r="D64" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="E64" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="G64" t="s">
         <v>172</v>
       </c>
       <c r="H64" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="I64" t="s">
         <v>35</v>
@@ -6304,16 +6301,16 @@
         <v>39</v>
       </c>
       <c r="N64" t="s">
-        <v>232</v>
+        <v>351</v>
       </c>
       <c r="O64" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="P64" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="Q64" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R64" t="s">
         <v>43</v>
@@ -6322,7 +6319,7 @@
         <v>43</v>
       </c>
       <c r="T64" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="U64" t="s">
         <v>35</v>
@@ -6334,39 +6331,39 @@
         <v>43</v>
       </c>
       <c r="X64">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="Y64">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="Z64" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="B65" t="s">
         <v>28</v>
       </c>
       <c r="C65" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="D65" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="E65" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="F65" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="G65" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="H65" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="I65" t="s">
         <v>35</v>
@@ -6384,13 +6381,13 @@
         <v>39</v>
       </c>
       <c r="N65" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="O65" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="P65" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="Q65" t="s">
         <v>43</v>
@@ -6402,7 +6399,7 @@
         <v>43</v>
       </c>
       <c r="T65" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="U65" t="s">
         <v>35</v>
@@ -6414,13 +6411,173 @@
         <v>43</v>
       </c>
       <c r="X65">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="Y65">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Z65" t="s">
-        <v>148</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>394</v>
+      </c>
+      <c r="B66" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" t="s">
+        <v>133</v>
+      </c>
+      <c r="D66" t="s">
+        <v>395</v>
+      </c>
+      <c r="E66" t="s">
+        <v>396</v>
+      </c>
+      <c r="F66" t="s">
+        <v>107</v>
+      </c>
+      <c r="G66" t="s">
+        <v>108</v>
+      </c>
+      <c r="H66" t="s">
+        <v>109</v>
+      </c>
+      <c r="I66" t="s">
+        <v>35</v>
+      </c>
+      <c r="J66" t="s">
+        <v>36</v>
+      </c>
+      <c r="K66" t="s">
+        <v>37</v>
+      </c>
+      <c r="L66" t="s">
+        <v>38</v>
+      </c>
+      <c r="M66" t="s">
+        <v>39</v>
+      </c>
+      <c r="N66" t="s">
+        <v>397</v>
+      </c>
+      <c r="O66" t="s">
+        <v>398</v>
+      </c>
+      <c r="P66" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>44</v>
+      </c>
+      <c r="R66" t="s">
+        <v>44</v>
+      </c>
+      <c r="S66" t="s">
+        <v>43</v>
+      </c>
+      <c r="T66" t="s">
+        <v>225</v>
+      </c>
+      <c r="U66" t="s">
+        <v>35</v>
+      </c>
+      <c r="V66" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" t="s">
+        <v>43</v>
+      </c>
+      <c r="X66">
+        <v>134</v>
+      </c>
+      <c r="Y66">
+        <v>115</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>400</v>
+      </c>
+      <c r="B67" t="s">
+        <v>81</v>
+      </c>
+      <c r="C67" t="s">
+        <v>49</v>
+      </c>
+      <c r="D67" t="s">
+        <v>401</v>
+      </c>
+      <c r="E67" t="s">
+        <v>402</v>
+      </c>
+      <c r="F67" t="s">
+        <v>96</v>
+      </c>
+      <c r="G67" t="s">
+        <v>52</v>
+      </c>
+      <c r="H67" t="s">
+        <v>53</v>
+      </c>
+      <c r="I67" t="s">
+        <v>35</v>
+      </c>
+      <c r="J67" t="s">
+        <v>36</v>
+      </c>
+      <c r="K67" t="s">
+        <v>37</v>
+      </c>
+      <c r="L67" t="s">
+        <v>38</v>
+      </c>
+      <c r="M67" t="s">
+        <v>39</v>
+      </c>
+      <c r="N67" t="s">
+        <v>403</v>
+      </c>
+      <c r="O67" t="s">
+        <v>404</v>
+      </c>
+      <c r="P67" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>44</v>
+      </c>
+      <c r="R67" t="s">
+        <v>44</v>
+      </c>
+      <c r="S67" t="s">
+        <v>43</v>
+      </c>
+      <c r="T67" t="s">
+        <v>79</v>
+      </c>
+      <c r="U67" t="s">
+        <v>35</v>
+      </c>
+      <c r="V67" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" t="s">
+        <v>43</v>
+      </c>
+      <c r="X67">
+        <v>150</v>
+      </c>
+      <c r="Y67">
+        <v>146</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
